--- a/test-attachments/mm-hybrid-workloads.xlsx
+++ b/test-attachments/mm-hybrid-workloads.xlsx
@@ -3,8 +3,8 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="On-Prem Baremetal" sheetId="1" r:id="rId1"/>
-    <sheet name="Core Networking" sheetId="2" r:id="rId2"/>
+    <sheet name="VMware Private Cloud" sheetId="1" r:id="rId1"/>
+    <sheet name="Top of Rack Switches" sheetId="2" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
@@ -398,671 +398,857 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:D51"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Hostname</v>
+        <v>VM Name</v>
       </c>
       <c r="B1" t="str">
-        <v>Serial</v>
+        <v>Cluster</v>
       </c>
       <c r="C1" t="str">
-        <v>Category</v>
+        <v>Memory GB</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Target Unit</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>bm-srv-1</v>
+        <v>esxi-vm-1</v>
       </c>
       <c r="B2" t="str">
-        <v>SN-1000</v>
+        <v>Cluster-Primary</v>
       </c>
       <c r="C2" t="str">
+        <v>64</v>
+      </c>
+      <c r="D2" t="str">
         <v>Host Server</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>bm-srv-2</v>
+        <v>esxi-vm-2</v>
       </c>
       <c r="B3" t="str">
-        <v>SN-1001</v>
+        <v>Cluster-Primary</v>
       </c>
       <c r="C3" t="str">
+        <v>64</v>
+      </c>
+      <c r="D3" t="str">
         <v>Host Server</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>bm-srv-3</v>
+        <v>esxi-vm-3</v>
       </c>
       <c r="B4" t="str">
-        <v>SN-1002</v>
+        <v>Cluster-Primary</v>
       </c>
       <c r="C4" t="str">
+        <v>64</v>
+      </c>
+      <c r="D4" t="str">
         <v>Host Server</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>bm-srv-4</v>
+        <v>esxi-vm-4</v>
       </c>
       <c r="B5" t="str">
-        <v>SN-1003</v>
+        <v>Cluster-Primary</v>
       </c>
       <c r="C5" t="str">
+        <v>64</v>
+      </c>
+      <c r="D5" t="str">
         <v>Host Server</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>bm-srv-5</v>
+        <v>esxi-vm-5</v>
       </c>
       <c r="B6" t="str">
-        <v>SN-1004</v>
+        <v>Cluster-Primary</v>
       </c>
       <c r="C6" t="str">
+        <v>64</v>
+      </c>
+      <c r="D6" t="str">
         <v>Host Server</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>bm-srv-6</v>
+        <v>esxi-vm-6</v>
       </c>
       <c r="B7" t="str">
-        <v>SN-1005</v>
+        <v>Cluster-Primary</v>
       </c>
       <c r="C7" t="str">
+        <v>64</v>
+      </c>
+      <c r="D7" t="str">
         <v>Host Server</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>bm-srv-7</v>
+        <v>esxi-vm-7</v>
       </c>
       <c r="B8" t="str">
-        <v>SN-1006</v>
+        <v>Cluster-Primary</v>
       </c>
       <c r="C8" t="str">
+        <v>64</v>
+      </c>
+      <c r="D8" t="str">
         <v>Host Server</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>bm-srv-8</v>
+        <v>esxi-vm-8</v>
       </c>
       <c r="B9" t="str">
-        <v>SN-1007</v>
+        <v>Cluster-Primary</v>
       </c>
       <c r="C9" t="str">
+        <v>64</v>
+      </c>
+      <c r="D9" t="str">
         <v>Host Server</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>bm-srv-9</v>
+        <v>esxi-vm-9</v>
       </c>
       <c r="B10" t="str">
-        <v>SN-1008</v>
+        <v>Cluster-Primary</v>
       </c>
       <c r="C10" t="str">
+        <v>64</v>
+      </c>
+      <c r="D10" t="str">
         <v>Host Server</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>bm-srv-10</v>
+        <v>esxi-vm-10</v>
       </c>
       <c r="B11" t="str">
-        <v>SN-1009</v>
+        <v>Cluster-Primary</v>
       </c>
       <c r="C11" t="str">
+        <v>64</v>
+      </c>
+      <c r="D11" t="str">
         <v>Host Server</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>bm-srv-11</v>
+        <v>esxi-vm-11</v>
       </c>
       <c r="B12" t="str">
-        <v>SN-1010</v>
+        <v>Cluster-Primary</v>
       </c>
       <c r="C12" t="str">
+        <v>64</v>
+      </c>
+      <c r="D12" t="str">
         <v>Host Server</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>bm-srv-12</v>
+        <v>esxi-vm-12</v>
       </c>
       <c r="B13" t="str">
-        <v>SN-1011</v>
+        <v>Cluster-Primary</v>
       </c>
       <c r="C13" t="str">
+        <v>64</v>
+      </c>
+      <c r="D13" t="str">
         <v>Host Server</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>bm-srv-13</v>
+        <v>esxi-vm-13</v>
       </c>
       <c r="B14" t="str">
-        <v>SN-1012</v>
+        <v>Cluster-Primary</v>
       </c>
       <c r="C14" t="str">
+        <v>64</v>
+      </c>
+      <c r="D14" t="str">
         <v>Host Server</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>bm-srv-14</v>
+        <v>esxi-vm-14</v>
       </c>
       <c r="B15" t="str">
-        <v>SN-1013</v>
+        <v>Cluster-Primary</v>
       </c>
       <c r="C15" t="str">
+        <v>64</v>
+      </c>
+      <c r="D15" t="str">
         <v>Host Server</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>bm-srv-15</v>
+        <v>esxi-vm-15</v>
       </c>
       <c r="B16" t="str">
-        <v>SN-1014</v>
+        <v>Cluster-Primary</v>
       </c>
       <c r="C16" t="str">
+        <v>64</v>
+      </c>
+      <c r="D16" t="str">
         <v>Host Server</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>bm-srv-16</v>
+        <v>esxi-vm-16</v>
       </c>
       <c r="B17" t="str">
-        <v>SN-1015</v>
+        <v>Cluster-Primary</v>
       </c>
       <c r="C17" t="str">
+        <v>64</v>
+      </c>
+      <c r="D17" t="str">
         <v>Host Server</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>bm-srv-17</v>
+        <v>esxi-vm-17</v>
       </c>
       <c r="B18" t="str">
-        <v>SN-1016</v>
+        <v>Cluster-Primary</v>
       </c>
       <c r="C18" t="str">
+        <v>64</v>
+      </c>
+      <c r="D18" t="str">
         <v>Host Server</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>bm-srv-18</v>
+        <v>esxi-vm-18</v>
       </c>
       <c r="B19" t="str">
-        <v>SN-1017</v>
+        <v>Cluster-Primary</v>
       </c>
       <c r="C19" t="str">
+        <v>64</v>
+      </c>
+      <c r="D19" t="str">
         <v>Host Server</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>bm-srv-19</v>
+        <v>esxi-vm-19</v>
       </c>
       <c r="B20" t="str">
-        <v>SN-1018</v>
+        <v>Cluster-Primary</v>
       </c>
       <c r="C20" t="str">
+        <v>64</v>
+      </c>
+      <c r="D20" t="str">
         <v>Host Server</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>bm-srv-20</v>
+        <v>esxi-vm-20</v>
       </c>
       <c r="B21" t="str">
-        <v>SN-1019</v>
+        <v>Cluster-Primary</v>
       </c>
       <c r="C21" t="str">
+        <v>64</v>
+      </c>
+      <c r="D21" t="str">
         <v>Host Server</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>bm-srv-21</v>
+        <v>esxi-vm-21</v>
       </c>
       <c r="B22" t="str">
-        <v>SN-1020</v>
+        <v>Cluster-Primary</v>
       </c>
       <c r="C22" t="str">
+        <v>64</v>
+      </c>
+      <c r="D22" t="str">
         <v>Host Server</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>bm-srv-22</v>
+        <v>esxi-vm-22</v>
       </c>
       <c r="B23" t="str">
-        <v>SN-1021</v>
+        <v>Cluster-Primary</v>
       </c>
       <c r="C23" t="str">
+        <v>64</v>
+      </c>
+      <c r="D23" t="str">
         <v>Host Server</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>bm-srv-23</v>
+        <v>esxi-vm-23</v>
       </c>
       <c r="B24" t="str">
-        <v>SN-1022</v>
+        <v>Cluster-Primary</v>
       </c>
       <c r="C24" t="str">
+        <v>64</v>
+      </c>
+      <c r="D24" t="str">
         <v>Host Server</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>bm-srv-24</v>
+        <v>esxi-vm-24</v>
       </c>
       <c r="B25" t="str">
-        <v>SN-1023</v>
+        <v>Cluster-Primary</v>
       </c>
       <c r="C25" t="str">
+        <v>64</v>
+      </c>
+      <c r="D25" t="str">
         <v>Host Server</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>bm-srv-25</v>
+        <v>esxi-vm-25</v>
       </c>
       <c r="B26" t="str">
-        <v>SN-1024</v>
+        <v>Cluster-Primary</v>
       </c>
       <c r="C26" t="str">
+        <v>64</v>
+      </c>
+      <c r="D26" t="str">
         <v>Host Server</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>bm-srv-26</v>
+        <v>esxi-vm-26</v>
       </c>
       <c r="B27" t="str">
-        <v>SN-1025</v>
+        <v>Cluster-Primary</v>
       </c>
       <c r="C27" t="str">
+        <v>64</v>
+      </c>
+      <c r="D27" t="str">
         <v>Host Server</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>bm-srv-27</v>
+        <v>esxi-vm-27</v>
       </c>
       <c r="B28" t="str">
-        <v>SN-1026</v>
+        <v>Cluster-Primary</v>
       </c>
       <c r="C28" t="str">
+        <v>64</v>
+      </c>
+      <c r="D28" t="str">
         <v>Host Server</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>bm-srv-28</v>
+        <v>esxi-vm-28</v>
       </c>
       <c r="B29" t="str">
-        <v>SN-1027</v>
+        <v>Cluster-Primary</v>
       </c>
       <c r="C29" t="str">
+        <v>64</v>
+      </c>
+      <c r="D29" t="str">
         <v>Host Server</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>bm-srv-29</v>
+        <v>esxi-vm-29</v>
       </c>
       <c r="B30" t="str">
-        <v>SN-1028</v>
+        <v>Cluster-Primary</v>
       </c>
       <c r="C30" t="str">
+        <v>64</v>
+      </c>
+      <c r="D30" t="str">
         <v>Host Server</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>bm-srv-30</v>
+        <v>esxi-vm-30</v>
       </c>
       <c r="B31" t="str">
-        <v>SN-1029</v>
+        <v>Cluster-Primary</v>
       </c>
       <c r="C31" t="str">
+        <v>64</v>
+      </c>
+      <c r="D31" t="str">
         <v>Host Server</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>bm-srv-31</v>
+        <v>esxi-vm-31</v>
       </c>
       <c r="B32" t="str">
-        <v>SN-1030</v>
+        <v>Cluster-Primary</v>
       </c>
       <c r="C32" t="str">
+        <v>64</v>
+      </c>
+      <c r="D32" t="str">
         <v>Host Server</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>bm-srv-32</v>
+        <v>esxi-vm-32</v>
       </c>
       <c r="B33" t="str">
-        <v>SN-1031</v>
+        <v>Cluster-Primary</v>
       </c>
       <c r="C33" t="str">
+        <v>64</v>
+      </c>
+      <c r="D33" t="str">
         <v>Host Server</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>bm-srv-33</v>
+        <v>esxi-vm-33</v>
       </c>
       <c r="B34" t="str">
-        <v>SN-1032</v>
+        <v>Cluster-Primary</v>
       </c>
       <c r="C34" t="str">
+        <v>64</v>
+      </c>
+      <c r="D34" t="str">
         <v>Host Server</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>bm-srv-34</v>
+        <v>esxi-vm-34</v>
       </c>
       <c r="B35" t="str">
-        <v>SN-1033</v>
+        <v>Cluster-Primary</v>
       </c>
       <c r="C35" t="str">
+        <v>64</v>
+      </c>
+      <c r="D35" t="str">
         <v>Host Server</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>bm-srv-35</v>
+        <v>esxi-vm-35</v>
       </c>
       <c r="B36" t="str">
-        <v>SN-1034</v>
+        <v>Cluster-Primary</v>
       </c>
       <c r="C36" t="str">
+        <v>64</v>
+      </c>
+      <c r="D36" t="str">
         <v>Host Server</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>bm-srv-36</v>
+        <v>esxi-vm-36</v>
       </c>
       <c r="B37" t="str">
-        <v>SN-1035</v>
+        <v>Cluster-Primary</v>
       </c>
       <c r="C37" t="str">
+        <v>64</v>
+      </c>
+      <c r="D37" t="str">
         <v>Host Server</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>bm-srv-37</v>
+        <v>esxi-vm-37</v>
       </c>
       <c r="B38" t="str">
-        <v>SN-1036</v>
+        <v>Cluster-Primary</v>
       </c>
       <c r="C38" t="str">
+        <v>64</v>
+      </c>
+      <c r="D38" t="str">
         <v>Host Server</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>bm-srv-38</v>
+        <v>esxi-vm-38</v>
       </c>
       <c r="B39" t="str">
-        <v>SN-1037</v>
+        <v>Cluster-Primary</v>
       </c>
       <c r="C39" t="str">
+        <v>64</v>
+      </c>
+      <c r="D39" t="str">
         <v>Host Server</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>bm-srv-39</v>
+        <v>esxi-vm-39</v>
       </c>
       <c r="B40" t="str">
-        <v>SN-1038</v>
+        <v>Cluster-Primary</v>
       </c>
       <c r="C40" t="str">
+        <v>64</v>
+      </c>
+      <c r="D40" t="str">
         <v>Host Server</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>bm-srv-40</v>
+        <v>esxi-vm-40</v>
       </c>
       <c r="B41" t="str">
-        <v>SN-1039</v>
+        <v>Cluster-Primary</v>
       </c>
       <c r="C41" t="str">
+        <v>64</v>
+      </c>
+      <c r="D41" t="str">
         <v>Host Server</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>bm-srv-41</v>
+        <v>esxi-vm-41</v>
       </c>
       <c r="B42" t="str">
-        <v>SN-1040</v>
+        <v>Cluster-Primary</v>
       </c>
       <c r="C42" t="str">
+        <v>64</v>
+      </c>
+      <c r="D42" t="str">
         <v>Host Server</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>bm-srv-42</v>
+        <v>esxi-vm-42</v>
       </c>
       <c r="B43" t="str">
-        <v>SN-1041</v>
+        <v>Cluster-Primary</v>
       </c>
       <c r="C43" t="str">
+        <v>64</v>
+      </c>
+      <c r="D43" t="str">
         <v>Host Server</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>bm-srv-43</v>
+        <v>esxi-vm-43</v>
       </c>
       <c r="B44" t="str">
-        <v>SN-1042</v>
+        <v>Cluster-Primary</v>
       </c>
       <c r="C44" t="str">
+        <v>64</v>
+      </c>
+      <c r="D44" t="str">
         <v>Host Server</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>bm-srv-44</v>
+        <v>esxi-vm-44</v>
       </c>
       <c r="B45" t="str">
-        <v>SN-1043</v>
+        <v>Cluster-Primary</v>
       </c>
       <c r="C45" t="str">
+        <v>64</v>
+      </c>
+      <c r="D45" t="str">
         <v>Host Server</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>bm-srv-45</v>
+        <v>esxi-vm-45</v>
       </c>
       <c r="B46" t="str">
-        <v>SN-1044</v>
+        <v>Cluster-Primary</v>
       </c>
       <c r="C46" t="str">
+        <v>64</v>
+      </c>
+      <c r="D46" t="str">
         <v>Host Server</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>bm-srv-46</v>
+        <v>esxi-vm-46</v>
       </c>
       <c r="B47" t="str">
-        <v>SN-1045</v>
+        <v>Cluster-Primary</v>
       </c>
       <c r="C47" t="str">
+        <v>64</v>
+      </c>
+      <c r="D47" t="str">
         <v>Host Server</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>bm-srv-47</v>
+        <v>esxi-vm-47</v>
       </c>
       <c r="B48" t="str">
-        <v>SN-1046</v>
+        <v>Cluster-Primary</v>
       </c>
       <c r="C48" t="str">
+        <v>64</v>
+      </c>
+      <c r="D48" t="str">
         <v>Host Server</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>bm-srv-48</v>
+        <v>esxi-vm-48</v>
       </c>
       <c r="B49" t="str">
-        <v>SN-1047</v>
+        <v>Cluster-Primary</v>
       </c>
       <c r="C49" t="str">
+        <v>64</v>
+      </c>
+      <c r="D49" t="str">
         <v>Host Server</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>bm-srv-49</v>
+        <v>esxi-vm-49</v>
       </c>
       <c r="B50" t="str">
-        <v>SN-1048</v>
+        <v>Cluster-Primary</v>
       </c>
       <c r="C50" t="str">
+        <v>64</v>
+      </c>
+      <c r="D50" t="str">
         <v>Host Server</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>bm-srv-50</v>
+        <v>esxi-vm-50</v>
       </c>
       <c r="B51" t="str">
-        <v>SN-1049</v>
+        <v>Cluster-Primary</v>
       </c>
       <c r="C51" t="str">
+        <v>64</v>
+      </c>
+      <c r="D51" t="str">
         <v>Host Server</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C51"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D51"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:C11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Device</v>
+        <v>Switch Name</v>
       </c>
       <c r="B1" t="str">
-        <v>Role</v>
+        <v>Location</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Target Unit</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>firewall-1</v>
+        <v>tor-sw-1</v>
       </c>
       <c r="B2" t="str">
-        <v>Network Component</v>
+        <v>Rack 01-10</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Network Switch</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>firewall-2</v>
+        <v>tor-sw-2</v>
       </c>
       <c r="B3" t="str">
-        <v>Network Component</v>
+        <v>Rack 01-10</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Network Switch</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>firewall-3</v>
+        <v>tor-sw-3</v>
       </c>
       <c r="B4" t="str">
-        <v>Network Component</v>
+        <v>Rack 01-10</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Network Switch</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>firewall-4</v>
+        <v>tor-sw-4</v>
       </c>
       <c r="B5" t="str">
-        <v>Network Component</v>
+        <v>Rack 01-10</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Network Switch</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>firewall-5</v>
+        <v>tor-sw-5</v>
       </c>
       <c r="B6" t="str">
-        <v>Network Component</v>
+        <v>Rack 01-10</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Network Switch</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>firewall-6</v>
+        <v>tor-sw-6</v>
       </c>
       <c r="B7" t="str">
-        <v>Network Component</v>
+        <v>Rack 01-10</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Network Switch</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>firewall-7</v>
+        <v>tor-sw-7</v>
       </c>
       <c r="B8" t="str">
-        <v>Network Component</v>
+        <v>Rack 01-10</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Network Switch</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>firewall-8</v>
+        <v>tor-sw-8</v>
       </c>
       <c r="B9" t="str">
-        <v>Network Component</v>
+        <v>Rack 01-10</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Network Switch</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>firewall-9</v>
+        <v>tor-sw-9</v>
       </c>
       <c r="B10" t="str">
-        <v>Network Component</v>
+        <v>Rack 01-10</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Network Switch</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>firewall-10</v>
+        <v>tor-sw-10</v>
       </c>
       <c r="B11" t="str">
-        <v>Network Component</v>
+        <v>Rack 01-10</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Network Switch</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C11"/>
   </ignoredErrors>
 </worksheet>
 </file>